--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0084.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0084.xlsx
@@ -6359,7 +6359,7 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>Và tất cả lũ Tacet Discord... ta sẽ biến vùng đất này trắng xóa bằng xương của chúng ngươi.</t>
+          <t>Và tất cả lũ Tacet Discord... ta sẽ biến vùng đất này trắng xóa bằng xương của chúng mày.</t>
         </is>
       </c>
     </row>
@@ -7919,7 +7919,7 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>Thủy Triều Hắc Ám kết nối tất cả chúng ta. Ta đã cảm nhận được sự hiện diện của {Male=hắn;Female=cô ấy}.</t>
+          <t>Thủy Triều Hắc Ám kết nối tất cả chúng ta. Ta đã cảm nhận được sự hiện diện của {Male=his;Female=her}.</t>
         </is>
       </c>
     </row>
@@ -7984,7 +7984,7 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>Giờ đây, {Male=anh ấy;Female=cô ấy} đã trở thành Kẻ Báo Điềm mới, bước trên con đường vốn... không dành cho {Male=mình;Female=mình} ấy.</t>
+          <t>Giờ đây, {Male=his;Female=hers} đã trở thành Kẻ Báo Điềm mới, bước trên con đường vốn... không dành cho {Male=his;Female=hers} ấy.</t>
         </is>
       </c>
     </row>
@@ -8049,7 +8049,7 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>Chính vì thế {Male=anh ấy;Female=cô ấy} cần chiếc đèn lồng này hơn ta nhiều.</t>
+          <t>Chính vì thế {Male=he;Female=she} cần chiếc đèn lồng này hơn ta nhiều.</t>
         </is>
       </c>
     </row>
@@ -9219,7 +9219,7 @@
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>Con đường của &lt;te href=260012&gt;Fenrico the First&lt;/te&gt;, thuộc Dòng Dõi Vực Sâu, đến đây là kết thúc.</t>
+          <t>Con đường của &lt;te href=260012&gt;Fenrico Đệ Nhất&lt;/te&gt;, thuộc Dòng Dõi Vực Sâu, đến đây là kết thúc.</t>
         </is>
       </c>
     </row>
@@ -12079,7 +12079,7 @@
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>Ta cũng muốn đích thân cảm ơn anh ấy.</t>
+          <t>Tao cũng muốn đích thân cảm ơn anh ấy.</t>
         </is>
       </c>
     </row>
@@ -13249,7 +13249,7 @@
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>Tiếc thật. Ta đã muốn thử xem có chặt đứt cái đầu dê đó chỉ bằng một nhát không.</t>
+          <t>Tiếc thật. Tao đã muốn thử xem có chặt đứt cái đầu dê đó chỉ bằng một nhát không.</t>
         </is>
       </c>
     </row>
@@ -13574,7 +13574,7 @@
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>Minh Đình à... Ta mới chỉ đến Kim Châu thôi.</t>
+          <t>Minh Đình à... Ta mới chỉ đến Jinzhou thôi.</t>
         </is>
       </c>
     </row>
@@ -13899,7 +13899,7 @@
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>Cậu vẫn đuổi theo hắn à?</t>
+          <t>Mày vẫn đuổi theo hắn à?</t>
         </is>
       </c>
     </row>
@@ -14159,7 +14159,7 @@
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t>Người ta gọi cậu là Rover, nhưng cậu không phải kẻ không nhà. Cậu là lưỡi kiếm đã có vỏ.</t>
+          <t>Người ta gọi cậu là Vận Mệnh Giả, nhưng cậu không phải kẻ không nhà. Cậu là lưỡi kiếm đã có vỏ.</t>
         </is>
       </c>
     </row>
@@ -16564,7 +16564,7 @@
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t>Nhiệm vụ của chúng ta là bảo vệ Septimont và người dân nơi đây. Chúng ta sẽ kiên守 ở đây, cho đến khi họ trở về trong vinh quang.</t>
+          <t>Nhiệm vụ của chúng ta là bảo vệ Septimont và người dân nơi đây. Chúng ta sẽ giữ vững ở đây, cho đến khi họ trở về trong vinh quang.</t>
         </is>
       </c>
     </row>
@@ -21504,7 +21504,7 @@
       </c>
       <c r="M324" t="inlineStr">
         <is>
-          <t>Chuyện gì đang xảy ra vậy?</t>
+          <t>Có chuyện gì vậy?</t>
         </is>
       </c>
     </row>
@@ -22284,7 +22284,7 @@
       </c>
       <c r="M336" t="inlineStr">
         <is>
-          <t>Đồ Threnodian chết tiệt! Ta về nhà nghỉ ngơi đây.</t>
+          <t>Đồ Threnodian chết tiệt! Tao về nhà nghỉ ngơi đây.</t>
         </is>
       </c>
     </row>
@@ -22804,7 +22804,7 @@
       </c>
       <c r="M344" t="inlineStr">
         <is>
-          <t>Những đứa trẻ này vẫn còn quá nhỏ để hiểu rằng những Tiếng Vang này là phước lành từ Imperator.</t>
+          <t>Những đứa trẻ này vẫn còn quá nhỏ để hiểu rằng những Echo này là phước lành từ Imperator.</t>
         </is>
       </c>
     </row>
@@ -23389,7 +23389,7 @@
       </c>
       <c r="M353" t="inlineStr">
         <is>
-          <t>Chuyện gì đã xảy ra?</t>
+          <t>Chuyện gì đã xảy ra thế?</t>
         </is>
       </c>
     </row>
@@ -23584,7 +23584,7 @@
       </c>
       <c r="M356" t="inlineStr">
         <is>
-          <t>Ragunna vừa trải qua Dark Tide, nhưng ta bảo này, mọi chuyện đều có lời giải khoa học cả.</t>
+          <t>Ragunna vừa trải qua Dark Tide, nhưng tao bảo này, mọi chuyện đều có lời giải khoa học cả.</t>
         </is>
       </c>
     </row>
@@ -23779,7 +23779,7 @@
       </c>
       <c r="M359" t="inlineStr">
         <is>
-          <t>Thề có Hoàng Đế! Có lẽ ta nên tống ngươi vào Nhà Tù Sám Hối ngay lập tức. Ngươi nên ở trên Thuyền Hành Hương mà ăn năn tội lỗi đi!</t>
+          <t>Thề có Hoàng Đế! Có lẽ tao nên tống mày vào Nhà Tù Sám Hối ngay lập tức. Mày nên ở trên Thuyền Hành Hương mà ăn năn tội lỗi đi!</t>
         </is>
       </c>
     </row>
@@ -24494,7 +24494,7 @@
       </c>
       <c r="M370" t="inlineStr">
         <is>
-          <t>Không đâu! Dạo này ta ngủ ngon lành luôn ấy chứ!</t>
+          <t>Không đâu! Dạo này tao ngủ ngon lành luôn ấy chứ!</t>
         </is>
       </c>
     </row>
@@ -26119,7 +26119,7 @@
       </c>
       <c r="M395" t="inlineStr">
         <is>
-          <t>Ta nghĩ Hiệp hội Tiên phong có thể giúp một tay. Nếu cậu quan tâm, sao không ghé qua studio của tụi ta trò chuyện khi cậu rảnh?</t>
+          <t>Tao nghĩ Hiệp hội Tiên phong có thể giúp một tay. Nếu cậu quan tâm, sao không ghé qua studio của tụi tao trò chuyện khi cậu rảnh?</t>
         </is>
       </c>
     </row>
@@ -28264,7 +28264,7 @@
       </c>
       <c r="M428" t="inlineStr">
         <is>
-          <t>Đầu ta vẫn còn đau... Ta đã cầu nguyện ở đây bao lâu rồi nhỉ?</t>
+          <t>Đầu tao vẫn còn đau... Tao đã cầu nguyện ở đây bao lâu rồi nhỉ?</t>
         </is>
       </c>
     </row>
@@ -29174,7 +29174,7 @@
       </c>
       <c r="M442" t="inlineStr">
         <is>
-          <t>Tụi ta không sao. Bọn Gladiator phản ứng nhanh, bảo vệ tất cả du khách an toàn.</t>
+          <t>Tụi tao không sao. Bọn Gladiator phản ứng nhanh, bảo vệ tất cả du khách an toàn.</t>
         </is>
       </c>
     </row>
@@ -31709,7 +31709,7 @@
       </c>
       <c r="M481" t="inlineStr">
         <is>
-          <t>Ta đã gửi thư cho những người bạn vẫn còn sống ở đó. Có lẽ hy vọng cuối cùng cũng đã đến gần...</t>
+          <t>Tao đã gửi thư cho những người bạn vẫn còn sống ở đó. Có lẽ hy vọng cuối cùng cũng đã đến gần...</t>
         </is>
       </c>
     </row>
@@ -32164,7 +32164,7 @@
       </c>
       <c r="M488" t="inlineStr">
         <is>
-          <t>Nhưng… liệu ta có nên về nhà thật không? Cô Anastasia và mọi người ở đây quan trọng với ta lắm…</t>
+          <t>Nhưng… liệu tao có nên về nhà thật không? Cô Anastasia và mọi người ở đây quan trọng với tao lắm…</t>
         </is>
       </c>
     </row>
@@ -32619,7 +32619,7 @@
       </c>
       <c r="M495" t="inlineStr">
         <is>
-          <t>Đừng nhìn ta với ánh mắt lo lắng thế. Ta ổn mà.</t>
+          <t>Đừng nhìn tao với ánh mắt lo lắng thế. Tao ổn mà.</t>
         </is>
       </c>
     </row>
